--- a/StructureDefinition-hiv-med-req.xlsx
+++ b/StructureDefinition-hiv-med-req.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T08:35:52+00:00</t>
+    <t>2023-05-03T08:46:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-med-req.xlsx
+++ b/StructureDefinition-hiv-med-req.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T08:46:45+00:00</t>
+    <t>2023-05-03T08:57:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -6144,10 +6144,10 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>81</v>

--- a/StructureDefinition-hiv-med-req.xlsx
+++ b/StructureDefinition-hiv-med-req.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T08:57:04+00:00</t>
+    <t>2023-05-03T08:57:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-med-req.xlsx
+++ b/StructureDefinition-hiv-med-req.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T08:57:52+00:00</t>
+    <t>2023-05-04T06:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-med-req.xlsx
+++ b/StructureDefinition-hiv-med-req.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T06:27:52+00:00</t>
+    <t>2023-05-04T12:38:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-med-req.xlsx
+++ b/StructureDefinition-hiv-med-req.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T12:38:34+00:00</t>
+    <t>2023-05-04T12:42:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-med-req.xlsx
+++ b/StructureDefinition-hiv-med-req.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T19:04:07+00:00</t>
+    <t>2023-05-05T19:04:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
